--- a/human_adjudication/human_adjudication_v_2_4_1/reviewer_runs/2025/R_Bulun/human_adjudication_v_2_4_1_2025_R_Bulun_completed.xlsx
+++ b/human_adjudication/human_adjudication_v_2_4_1/reviewer_runs/2025/R_Bulun/human_adjudication_v_2_4_1_2025_R_Bulun_completed.xlsx
@@ -26,6 +26,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C_jama.2024.24764'!$A$1:$R$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'C_jama.2024.27643'!$A$1:$R$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'C_jama.2025.11178'!$A$1:$R$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'C_jama.2025.15185'!$A$1:$R$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'C_jama.2025.15440'!$A$1:$R$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'C_jama.2025.16450'!$A$1:$R$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'C_jama.2025.19563'!$A$1:$R$14</definedName>
@@ -129,7 +131,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
@@ -226,7 +228,6 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -9431,7 +9432,7 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>109</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" ht="55" customFormat="1" customHeight="1" s="14">
@@ -9441,7 +9442,7 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('C_jama.2024.24764'!$G$2:$G$6,"PRIMARY READY")+COUNTIF('C_jama.2024.27643'!$G$2:$G$17,"PRIMARY READY")+COUNTIF('C_jama.2025.15440'!$G$2:$G$2,"PRIMARY READY")+COUNTIF('C_jama.2025.16450'!$G$2:$G$7,"PRIMARY READY")+COUNTIF('C_jama.2025.19563'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.19843'!$G$2:$G$8,"PRIMARY READY")+COUNTIF('C_jama.2025.20765'!$G$2:$G$20,"PRIMARY READY")+COUNTIF('C_jama.2025.24175'!$G$2:$G$15,"PRIMARY READY")+COUNTIF('C_jama.2025.4390'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.7583'!$G$2:$G$5,"PRIMARY READY")+COUNTIF('C_jama.2025.7710'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9110'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9663'!$G$2:$G$6,"PRIMARY READY")</f>
+        <f>COUNTIF('C_jama.2024.24764'!$G$2:$G$6,"PRIMARY READY")+COUNTIF('C_jama.2024.27643'!$G$2:$G$17,"PRIMARY READY")+COUNTIF('C_jama.2025.11178'!$G$2:$G$19,"PRIMARY READY")+COUNTIF('C_jama.2025.15185'!$G$2:$G$7,"PRIMARY READY")+COUNTIF('C_jama.2025.15440'!$G$2:$G$2,"PRIMARY READY")+COUNTIF('C_jama.2025.16450'!$G$2:$G$7,"PRIMARY READY")+COUNTIF('C_jama.2025.19563'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.19843'!$G$2:$G$8,"PRIMARY READY")+COUNTIF('C_jama.2025.20765'!$G$2:$G$20,"PRIMARY READY")+COUNTIF('C_jama.2025.24175'!$G$2:$G$15,"PRIMARY READY")+COUNTIF('C_jama.2025.4390'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.7583'!$G$2:$G$5,"PRIMARY READY")+COUNTIF('C_jama.2025.7710'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9110'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9663'!$G$2:$G$6,"PRIMARY READY")</f>
         <v/>
       </c>
     </row>
@@ -9452,7 +9453,7 @@
         </is>
       </c>
       <c r="B5" s="17">
-        <f>COUNTIF('C_jama.2024.24764'!$D$2:$D$6,"discuss")+COUNTIF('C_jama.2024.27643'!$D$2:$D$17,"discuss")+COUNTIF('C_jama.2025.15440'!$D$2:$D$2,"discuss")+COUNTIF('C_jama.2025.16450'!$D$2:$D$7,"discuss")+COUNTIF('C_jama.2025.19563'!$D$2:$D$14,"discuss")+COUNTIF('C_jama.2025.19843'!$D$2:$D$8,"discuss")+COUNTIF('C_jama.2025.20765'!$D$2:$D$20,"discuss")+COUNTIF('C_jama.2025.24175'!$D$2:$D$15,"discuss")+COUNTIF('C_jama.2025.4390'!$D$2:$D$14,"discuss")+COUNTIF('C_jama.2025.7583'!$D$2:$D$5,"discuss")+COUNTIF('C_jama.2025.7710'!$D$2:$D$4,"discuss")+COUNTIF('C_jama.2025.9110'!$D$2:$D$4,"discuss")+COUNTIF('C_jama.2025.9663'!$D$2:$D$6,"discuss")</f>
+        <f>COUNTIF('C_jama.2024.24764'!$D$2:$D$6,"discuss")+COUNTIF('C_jama.2024.27643'!$D$2:$D$17,"discuss")+COUNTIF('C_jama.2025.11178'!$D$2:$D$19,"discuss")+COUNTIF('C_jama.2025.15185'!$D$2:$D$7,"discuss")+COUNTIF('C_jama.2025.15440'!$D$2:$D$2,"discuss")+COUNTIF('C_jama.2025.16450'!$D$2:$D$7,"discuss")+COUNTIF('C_jama.2025.19563'!$D$2:$D$14,"discuss")+COUNTIF('C_jama.2025.19843'!$D$2:$D$8,"discuss")+COUNTIF('C_jama.2025.20765'!$D$2:$D$20,"discuss")+COUNTIF('C_jama.2025.24175'!$D$2:$D$15,"discuss")+COUNTIF('C_jama.2025.4390'!$D$2:$D$14,"discuss")+COUNTIF('C_jama.2025.7583'!$D$2:$D$5,"discuss")+COUNTIF('C_jama.2025.7710'!$D$2:$D$4,"discuss")+COUNTIF('C_jama.2025.9110'!$D$2:$D$4,"discuss")+COUNTIF('C_jama.2025.9663'!$D$2:$D$6,"discuss")</f>
         <v/>
       </c>
     </row>
@@ -9513,13 +9514,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" style="14" min="1" max="1"/>
     <col width="38" customWidth="1" style="14" min="2" max="2"/>
     <col width="18" customWidth="1" style="14" min="3" max="3"/>
-    <col width="60" customWidth="1" style="25" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customFormat="1" customHeight="1" s="14">
@@ -9538,11 +9538,6 @@
           <t>Candidates</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="36" customHeight="1" s="25">
       <c r="A2" s="16" t="inlineStr">
@@ -9586,12 +9581,7 @@
         </is>
       </c>
       <c r="C4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>Placeholder: workflow 1.6.2 output pending; no candidates in this version</t>
-        </is>
+        <v>18</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" s="25">
@@ -9606,12 +9596,7 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Placeholder: workflow 1.6.2 output pending; no candidates in this version</t>
-        </is>
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" s="25">
@@ -11530,7 +11515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="14" min="1" max="1"/>
@@ -11625,15 +11610,1295 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="26" t="inlineStr">
-        <is>
-          <t>Placeholder: no workflow 1.6.2 output for this paper yet; nothing to review in v.2.4.1.</t>
+    <row r="2" ht="92" customHeight="1" s="25">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C001</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Planned versus reported online session duration</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Yes, all five locations: REPORT main p.3, Health Coach Program and Online Program — jama_debar_2025_oi_250046_1755300121.13587.pdf; PLAN protocol p.43 §10.1.1 — joi250046supp1_prod_1755300121.14087.pdf and p.44 coach overview — joi250046supp1_prod_1755300121.14087.pdf; REPORT TIDieR p.3 Procedures — joi250046supp3_prod_1755300121.15087.pdf and p.4 When and How Much — joi250046supp3_prod_1755300121.15087.pdf.</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G2" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A2="",COUNTIF($A$2:$A$19,A2)&lt;&gt;1,LEFT(A2,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D2="retain",E2="statistical_results")),H2&lt;&gt;"",NOT(EXACT(H2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),I2&lt;&gt;"",NOT(EXACT(I2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),J2&lt;&gt;"",NOT(EXACT(J2,"not_applicable"))),AND(NOT(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material"))),K2&lt;&gt;"",NOT(EXACT(K2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="protocol_report")),L2&lt;&gt;"",NOT(EXACT(L2,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D2,"retain"),EXACT(D2,"exclude"),EXACT(D2,"discuss"))),NOT(OR(EXACT(E2,"statistical_results"),EXACT(E2,"report_internal_inconsistency"),EXACT(E2,"plan_material"),EXACT(E2,"protocol_report"))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(H2,"confirmed_issue"),EXACT(H2,"probable_issue"),EXACT(H2,"not_issue"),EXACT(H2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(I2,"substantive"),EXACT(I2,"minor_presentation"),EXACT(I2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),J2&lt;&gt;"",NOT(OR(EXACT(J2,"direct"),EXACT(J2,"possible"),EXACT(J2,"unlikely"),EXACT(J2,"unknown")))),AND(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material")),NOT(OR(EXACT(K2,"substantive_inconsistency"),EXACT(K2,"minor_presentation"),EXACT(K2,"non_inconsistency"),EXACT(K2,"indeterminate")))),AND(AND(D2="retain",E2="protocol_report"),L2&lt;&gt;"",NOT(OR(EXACT(L2,"substantive_difference"),EXACT(L2,"minor_presentation"),EXACT(L2,"version_timing"),EXACT(L2,"non_inconsistency"),EXACT(L2,"indeterminate"))))),"CHECK FIELDS",IF(AND(F2&lt;&gt;"",NOT(OR(EXACT(F2,"no"),EXACT(F2,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F2,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J2" s="22">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),OR(E2="report_internal_inconsistency",E2="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L2" s="22" t="inlineStr">
+        <is>
+          <t>indeterminate</t>
+        </is>
+      </c>
+      <c r="M2" s="20" t="n"/>
+      <c r="N2" s="23" t="n"/>
+      <c r="O2" s="23" t="n"/>
+      <c r="P2" s="23" t="n"/>
+      <c r="Q2" s="23" t="n"/>
+      <c r="R2" s="22" t="inlineStr">
+        <is>
+          <t>Protocol v5.0 p.43 (§10.1.1) says each painTRAINER session takes 45-60 min and p.44 says coach sessions take 60 min; main p.3 and TIDieR Supp3 pp.3-4 give 30-45 min (online) and 45-60 min (coach). Real plan-report difference in described session dose; whether content changed or only the time estimate is not stated, so L indeterminate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="92" customHeight="1" s="25">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C002</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Therapeutic-dose adherence percentage</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.4 Results adherence paragraph — jama_debar_2025_oi_250046_1755300121.13587.pdf and p.5 Figure 1 PT allocation/session counts — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G3" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A3="",COUNTIF($A$2:$A$19,A3)&lt;&gt;1,LEFT(A3,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D3="retain",E3="statistical_results")),H3&lt;&gt;"",NOT(EXACT(H3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),I3&lt;&gt;"",NOT(EXACT(I3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),J3&lt;&gt;"",NOT(EXACT(J3,"not_applicable"))),AND(NOT(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material"))),K3&lt;&gt;"",NOT(EXACT(K3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="protocol_report")),L3&lt;&gt;"",NOT(EXACT(L3,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D3,"retain"),EXACT(D3,"exclude"),EXACT(D3,"discuss"))),NOT(OR(EXACT(E3,"statistical_results"),EXACT(E3,"report_internal_inconsistency"),EXACT(E3,"plan_material"),EXACT(E3,"protocol_report"))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(H3,"confirmed_issue"),EXACT(H3,"probable_issue"),EXACT(H3,"not_issue"),EXACT(H3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(I3,"substantive"),EXACT(I3,"minor_presentation"),EXACT(I3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),J3&lt;&gt;"",NOT(OR(EXACT(J3,"direct"),EXACT(J3,"possible"),EXACT(J3,"unlikely"),EXACT(J3,"unknown")))),AND(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material")),NOT(OR(EXACT(K3,"substantive_inconsistency"),EXACT(K3,"minor_presentation"),EXACT(K3,"non_inconsistency"),EXACT(K3,"indeterminate")))),AND(AND(D3="retain",E3="protocol_report"),L3&lt;&gt;"",NOT(OR(EXACT(L3,"substantive_difference"),EXACT(L3,"minor_presentation"),EXACT(L3,"version_timing"),EXACT(L3,"non_inconsistency"),EXACT(L3,"indeterminate"))))),"CHECK FIELDS",IF(AND(F3&lt;&gt;"",NOT(OR(EXACT(F3,"no"),EXACT(F3,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F3,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I3" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J3" s="22" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="K3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),OR(E3="report_internal_inconsistency",E3="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L3" s="22">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M3" s="24" t="n"/>
+      <c r="N3" s="23" t="n"/>
+      <c r="O3" s="23" t="n"/>
+      <c r="P3" s="23" t="n"/>
+      <c r="Q3" s="23" t="n"/>
+      <c r="R3" s="22" t="inlineStr">
+        <is>
+          <t>Main p.4: painTRAINER '371 (43%) completed at least 6 sessions'; Figure 1 (p.5) gives 776 randomized, 371/156/249 completing 6-8/1-5/0 sessions. 371/776 = 47.8% (printed 43%). Neighbors reproduce: 527/776 = 67.9% (68%), 548/778 = 70.4% (70%), 660/778 = 84.8% (85%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="92" customHeight="1" s="25">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C003</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>SMD construction across Table 3</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.4 SMD definition — jama_debar_2025_oi_250046_1755300121.13587.pdf, p.10 Table 3 — jama_debar_2025_oi_250046_1755300121.13587.pdf, and p.11 continuation and footnote d — jama_debar_2025_oi_250046_1755300121.13587.pdf. All twenty registered outcome/time rows and all three point-contrast columns per row were read directly.</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G4" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A4="",COUNTIF($A$2:$A$19,A4)&lt;&gt;1,LEFT(A4,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D4="retain",E4="statistical_results")),H4&lt;&gt;"",NOT(EXACT(H4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),I4&lt;&gt;"",NOT(EXACT(I4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),J4&lt;&gt;"",NOT(EXACT(J4,"not_applicable"))),AND(NOT(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material"))),K4&lt;&gt;"",NOT(EXACT(K4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="protocol_report")),L4&lt;&gt;"",NOT(EXACT(L4,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D4,"retain"),EXACT(D4,"exclude"),EXACT(D4,"discuss"))),NOT(OR(EXACT(E4,"statistical_results"),EXACT(E4,"report_internal_inconsistency"),EXACT(E4,"plan_material"),EXACT(E4,"protocol_report"))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(H4,"confirmed_issue"),EXACT(H4,"probable_issue"),EXACT(H4,"not_issue"),EXACT(H4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(I4,"substantive"),EXACT(I4,"minor_presentation"),EXACT(I4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),J4&lt;&gt;"",NOT(OR(EXACT(J4,"direct"),EXACT(J4,"possible"),EXACT(J4,"unlikely"),EXACT(J4,"unknown")))),AND(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material")),NOT(OR(EXACT(K4,"substantive_inconsistency"),EXACT(K4,"minor_presentation"),EXACT(K4,"non_inconsistency"),EXACT(K4,"indeterminate")))),AND(AND(D4="retain",E4="protocol_report"),L4&lt;&gt;"",NOT(OR(EXACT(L4,"substantive_difference"),EXACT(L4,"minor_presentation"),EXACT(L4,"version_timing"),EXACT(L4,"non_inconsistency"),EXACT(L4,"indeterminate"))))),"CHECK FIELDS",IF(AND(F4&lt;&gt;"",NOT(OR(EXACT(F4,"no"),EXACT(F4,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F4,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>substantive</t>
+        </is>
+      </c>
+      <c r="J4" s="22" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),OR(E4="report_internal_inconsistency",E4="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L4" s="22">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M4" s="20" t="n"/>
+      <c r="N4" s="23" t="n"/>
+      <c r="O4" s="23" t="n"/>
+      <c r="P4" s="23" t="n"/>
+      <c r="Q4" s="23" t="n"/>
+      <c r="R4" s="22" t="inlineStr">
+        <is>
+          <t>Main p.4 and Table 3 footnote d define SMD = adjusted MD / SD of change in usual care at that time, so within a row the three SMDs share one SD. For 19 of 21 rows (pp.10-11) no single SD reproduces all three SMDs from the printed MDs within rounding; 4 SMDs have the opposite sign to their MD (eg physical 3 mo HC vs UC MD 0.7, SMD -0.02). Text p.7 also cites 3-month SMDs -0.26/-0.36, which are the 6-month values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1" s="25">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C004</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Reciprocal NNT point-reproduction pattern</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.4 NNT definition — jama_debar_2025_oi_250046_1755300121.13587.pdf; REPORT main p.9 Table 2 severity 6-month HC/UC, interference 6-month HC/UC and footnote d — jama_debar_2025_oi_250046_1755300121.13587.pdf; REPORT results p.14 eTable 8 reminder-letter 6-month PT/UC and footnote d — joi250046supp4_prod_1755300121.15587.pdf. All three affected rows were read.</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G5" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A5="",COUNTIF($A$2:$A$19,A5)&lt;&gt;1,LEFT(A5,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D5="retain",E5="statistical_results")),H5&lt;&gt;"",NOT(EXACT(H5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),I5&lt;&gt;"",NOT(EXACT(I5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),J5&lt;&gt;"",NOT(EXACT(J5,"not_applicable"))),AND(NOT(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material"))),K5&lt;&gt;"",NOT(EXACT(K5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="protocol_report")),L5&lt;&gt;"",NOT(EXACT(L5,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D5,"retain"),EXACT(D5,"exclude"),EXACT(D5,"discuss"))),NOT(OR(EXACT(E5,"statistical_results"),EXACT(E5,"report_internal_inconsistency"),EXACT(E5,"plan_material"),EXACT(E5,"protocol_report"))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(H5,"confirmed_issue"),EXACT(H5,"probable_issue"),EXACT(H5,"not_issue"),EXACT(H5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(I5,"substantive"),EXACT(I5,"minor_presentation"),EXACT(I5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),J5&lt;&gt;"",NOT(OR(EXACT(J5,"direct"),EXACT(J5,"possible"),EXACT(J5,"unlikely"),EXACT(J5,"unknown")))),AND(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material")),NOT(OR(EXACT(K5,"substantive_inconsistency"),EXACT(K5,"minor_presentation"),EXACT(K5,"non_inconsistency"),EXACT(K5,"indeterminate")))),AND(AND(D5="retain",E5="protocol_report"),L5&lt;&gt;"",NOT(OR(EXACT(L5,"substantive_difference"),EXACT(L5,"minor_presentation"),EXACT(L5,"version_timing"),EXACT(L5,"non_inconsistency"),EXACT(L5,"indeterminate"))))),"CHECK FIELDS",IF(AND(F5&lt;&gt;"",NOT(OR(EXACT(F5,"no"),EXACT(F5,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F5,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J5" s="22">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),OR(E5="report_internal_inconsistency",E5="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L5" s="22">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M5" s="24" t="n"/>
+      <c r="N5" s="23" t="n"/>
+      <c r="O5" s="23" t="n"/>
+      <c r="P5" s="23" t="n"/>
+      <c r="Q5" s="23" t="n"/>
+      <c r="R5" s="22" t="inlineStr">
+        <is>
+          <t>NNT points are consistently rounded up (ceiling), the usual NNT convention: ceiling of 100/(difference in printed adjusted %) reproduces all 57 positive NNT points in Table 2 (main p.9) and eTables 7-8 (Supp4 pp.11, 14) within display rounding, whereas round-to-nearest fails 22 of 57. The three flagged cells (8, 7, 8) fit ceiling (7.04-&gt;8, 6.02-&gt;7, 7.04-&gt;8). Convention unstated but explains the pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92" customHeight="1" s="25">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C005</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Age as a prespecified base adjustment covariate</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Yes: PLAN protocol p.56 §15.5 — joi250046supp1_prod_1755300121.14087.pdf; PLAN SAP p.20 §§13–14 — joi250046supp2_prod_1755300121.15087.pdf; REPORT main p.4 adjustment sentence — jama_debar_2025_oi_250046_1755300121.13587.pdf; REPORT results p.4 Adjustment — joi250046supp4_prod_1755300121.15587.pdf, p.7 eTable 2 all-model variables — joi250046supp4_prod_1755300121.15587.pdf, p.8 eTable 3 age — joi250046supp4_prod_1755300121.15587.pdf, p.9 eTable 4 age — joi250046supp4_prod_1755300121.15587.pdf, p.10 eTable 5 age — joi250046supp4_prod_1755300121.15587.pdf; REPORT workbook — joi250046supp5_prod_1755300121.16087.xlsx, worksheet eTable 3, cells G2, A10, G10, directly decoded.</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G6" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A6="",COUNTIF($A$2:$A$19,A6)&lt;&gt;1,LEFT(A6,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D6="retain",E6="statistical_results")),H6&lt;&gt;"",NOT(EXACT(H6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),I6&lt;&gt;"",NOT(EXACT(I6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),J6&lt;&gt;"",NOT(EXACT(J6,"not_applicable"))),AND(NOT(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material"))),K6&lt;&gt;"",NOT(EXACT(K6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="protocol_report")),L6&lt;&gt;"",NOT(EXACT(L6,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D6,"retain"),EXACT(D6,"exclude"),EXACT(D6,"discuss"))),NOT(OR(EXACT(E6,"statistical_results"),EXACT(E6,"report_internal_inconsistency"),EXACT(E6,"plan_material"),EXACT(E6,"protocol_report"))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(H6,"confirmed_issue"),EXACT(H6,"probable_issue"),EXACT(H6,"not_issue"),EXACT(H6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(I6,"substantive"),EXACT(I6,"minor_presentation"),EXACT(I6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),J6&lt;&gt;"",NOT(OR(EXACT(J6,"direct"),EXACT(J6,"possible"),EXACT(J6,"unlikely"),EXACT(J6,"unknown")))),AND(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material")),NOT(OR(EXACT(K6,"substantive_inconsistency"),EXACT(K6,"minor_presentation"),EXACT(K6,"non_inconsistency"),EXACT(K6,"indeterminate")))),AND(AND(D6="retain",E6="protocol_report"),L6&lt;&gt;"",NOT(OR(EXACT(L6,"substantive_difference"),EXACT(L6,"minor_presentation"),EXACT(L6,"version_timing"),EXACT(L6,"non_inconsistency"),EXACT(L6,"indeterminate"))))),"CHECK FIELDS",IF(AND(F6&lt;&gt;"",NOT(OR(EXACT(F6,"no"),EXACT(F6,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F6,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J6" s="22">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),OR(E6="report_internal_inconsistency",E6="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>substantive_difference</t>
+        </is>
+      </c>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="23" t="n"/>
+      <c r="O6" s="23" t="n"/>
+      <c r="P6" s="23" t="n"/>
+      <c r="Q6" s="23" t="n"/>
+      <c r="R6" s="22" t="inlineStr">
+        <is>
+          <t>Protocol §15.5 (p.56) and SAP v6.0 §14 (p.20) list prespecified primary covariates as baseline pain severity, sex, site, rural/underserved residence, multisite pain and mental-health condition (no age), as does main p.4; Supp4 p.4, eTable 2 (p.7) and workbook eTable 3 (G10 'X') call age &gt;=65 part of the prespecified base set, and age is fitted in eTables 3-5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1" s="25">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C006</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Secondary-analysis adjustment specification</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>Yes: PLAN protocol p.57 §15.6 — joi250046supp1_prod_1755300121.14087.pdf; PLAN SAP p.21 §15 — joi250046supp2_prod_1755300121.15087.pdf; REPORT main p.4 secondary methods — jama_debar_2025_oi_250046_1755300121.13587.pdf, p.10 Table 3 — jama_debar_2025_oi_250046_1755300121.13587.pdf and p.11 continuation — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G7" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A7="",COUNTIF($A$2:$A$19,A7)&lt;&gt;1,LEFT(A7,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D7="retain",E7="statistical_results")),H7&lt;&gt;"",NOT(EXACT(H7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),I7&lt;&gt;"",NOT(EXACT(I7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),J7&lt;&gt;"",NOT(EXACT(J7,"not_applicable"))),AND(NOT(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material"))),K7&lt;&gt;"",NOT(EXACT(K7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="protocol_report")),L7&lt;&gt;"",NOT(EXACT(L7,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D7,"retain"),EXACT(D7,"exclude"),EXACT(D7,"discuss"))),NOT(OR(EXACT(E7,"statistical_results"),EXACT(E7,"report_internal_inconsistency"),EXACT(E7,"plan_material"),EXACT(E7,"protocol_report"))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(H7,"confirmed_issue"),EXACT(H7,"probable_issue"),EXACT(H7,"not_issue"),EXACT(H7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(I7,"substantive"),EXACT(I7,"minor_presentation"),EXACT(I7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),J7&lt;&gt;"",NOT(OR(EXACT(J7,"direct"),EXACT(J7,"possible"),EXACT(J7,"unlikely"),EXACT(J7,"unknown")))),AND(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material")),NOT(OR(EXACT(K7,"substantive_inconsistency"),EXACT(K7,"minor_presentation"),EXACT(K7,"non_inconsistency"),EXACT(K7,"indeterminate")))),AND(AND(D7="retain",E7="protocol_report"),L7&lt;&gt;"",NOT(OR(EXACT(L7,"substantive_difference"),EXACT(L7,"minor_presentation"),EXACT(L7,"version_timing"),EXACT(L7,"non_inconsistency"),EXACT(L7,"indeterminate"))))),"CHECK FIELDS",IF(AND(F7&lt;&gt;"",NOT(OR(EXACT(F7,"no"),EXACT(F7,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F7,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J7" s="22">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),OR(E7="report_internal_inconsistency",E7="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L7" s="22" t="inlineStr">
+        <is>
+          <t>substantive_difference</t>
+        </is>
+      </c>
+      <c r="M7" s="24" t="n"/>
+      <c r="N7" s="23" t="n"/>
+      <c r="O7" s="23" t="n"/>
+      <c r="P7" s="23" t="n"/>
+      <c r="Q7" s="23" t="n"/>
+      <c r="R7" s="22" t="inlineStr">
+        <is>
+          <t>Protocol §15.6 (p.57) and SAP §15 (p.21): secondary analyses adjust for baseline pain severity and all stratification variables. Main p.4: secondary outcomes use the primary model structure (adding multisite pain, mental-health condition) plus the baseline value of each secondary outcome. Covariate set differs from plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="92" customHeight="1" s="25">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C007</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>Primary versus sensitivity missing-data analysis roles</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>Yes: PLAN SAP p.19 §11 — joi250046supp2_prod_1755300121.15087.pdf, PLAN p.4 July 17, 2024 amendment — joi250046supp2_prod_1755300121.15087.pdf; REPORT main p.4 missing-data paragraph — jama_debar_2025_oi_250046_1755300121.13587.pdf; REPORT results p.4 Missing Data — joi250046supp4_prod_1755300121.15587.pdf, p.5 Non-Response Weighting — joi250046supp4_prod_1755300121.15587.pdf, p.9 eTable 4 — joi250046supp4_prod_1755300121.15587.pdf, p.11 sensitivity narrative and complete-case block — joi250046supp4_prod_1755300121.15587.pdf. P.5 was read as disclosed-amendment context in addition to the registered comparisons.</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G8" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A8="",COUNTIF($A$2:$A$19,A8)&lt;&gt;1,LEFT(A8,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D8="retain",E8="statistical_results")),H8&lt;&gt;"",NOT(EXACT(H8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),I8&lt;&gt;"",NOT(EXACT(I8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),J8&lt;&gt;"",NOT(EXACT(J8,"not_applicable"))),AND(NOT(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material"))),K8&lt;&gt;"",NOT(EXACT(K8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="protocol_report")),L8&lt;&gt;"",NOT(EXACT(L8,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D8,"retain"),EXACT(D8,"exclude"),EXACT(D8,"discuss"))),NOT(OR(EXACT(E8,"statistical_results"),EXACT(E8,"report_internal_inconsistency"),EXACT(E8,"plan_material"),EXACT(E8,"protocol_report"))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(H8,"confirmed_issue"),EXACT(H8,"probable_issue"),EXACT(H8,"not_issue"),EXACT(H8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(I8,"substantive"),EXACT(I8,"minor_presentation"),EXACT(I8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),J8&lt;&gt;"",NOT(OR(EXACT(J8,"direct"),EXACT(J8,"possible"),EXACT(J8,"unlikely"),EXACT(J8,"unknown")))),AND(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material")),NOT(OR(EXACT(K8,"substantive_inconsistency"),EXACT(K8,"minor_presentation"),EXACT(K8,"non_inconsistency"),EXACT(K8,"indeterminate")))),AND(AND(D8="retain",E8="protocol_report"),L8&lt;&gt;"",NOT(OR(EXACT(L8,"substantive_difference"),EXACT(L8,"minor_presentation"),EXACT(L8,"version_timing"),EXACT(L8,"non_inconsistency"),EXACT(L8,"indeterminate"))))),"CHECK FIELDS",IF(AND(F8&lt;&gt;"",NOT(OR(EXACT(F8,"no"),EXACT(F8,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F8,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H8" s="21">
+        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I8" s="21">
+        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J8" s="22">
+        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K8" s="21">
+        <f>IF(AND(OR(D8="retain",D8=""),OR(E8="report_internal_inconsistency",E8="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>substantive_difference</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="n"/>
+      <c r="N8" s="23" t="n"/>
+      <c r="O8" s="23" t="n"/>
+      <c r="P8" s="23" t="n"/>
+      <c r="Q8" s="23" t="n"/>
+      <c r="R8" s="22" t="inlineStr">
+        <is>
+          <t>SAP v6.0 §11 (p.19): 'For the primary analyses, we will analyze those patients who have follow-up data' under MAR; pattern-mixture plus IPW is the 'first approach' when missingness &gt;15%, worst/best case the sensitivity analysis. Report (main p.4; Supp4 pp.4-5, eTables 4 and 7) makes MNAR pattern-mixture with IPW the primary analysis and labels complete-case a 'pre-specified sensitivity analysis'. IPW added by 17 Jul 2024 amendment (SAP p.4), after follow-up ended; disclosed Supp4 p.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="92" customHeight="1" s="25">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C008</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>RR versus finite NNT null coverage</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.9 Table 2 HC/PT columns and footnotes b,d,e — jama_debar_2025_oi_250046_1755300121.13587.pdf, all six registered contrast/time rows; REPORT p.4 binary model and NNT method — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G9" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A9="",COUNTIF($A$2:$A$19,A9)&lt;&gt;1,LEFT(A9,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D9="retain",E9="statistical_results")),H9&lt;&gt;"",NOT(EXACT(H9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),I9&lt;&gt;"",NOT(EXACT(I9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),J9&lt;&gt;"",NOT(EXACT(J9,"not_applicable"))),AND(NOT(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material"))),K9&lt;&gt;"",NOT(EXACT(K9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="protocol_report")),L9&lt;&gt;"",NOT(EXACT(L9,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D9,"retain"),EXACT(D9,"exclude"),EXACT(D9,"discuss"))),NOT(OR(EXACT(E9,"statistical_results"),EXACT(E9,"report_internal_inconsistency"),EXACT(E9,"plan_material"),EXACT(E9,"protocol_report"))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(H9,"confirmed_issue"),EXACT(H9,"probable_issue"),EXACT(H9,"not_issue"),EXACT(H9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(I9,"substantive"),EXACT(I9,"minor_presentation"),EXACT(I9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),J9&lt;&gt;"",NOT(OR(EXACT(J9,"direct"),EXACT(J9,"possible"),EXACT(J9,"unlikely"),EXACT(J9,"unknown")))),AND(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material")),NOT(OR(EXACT(K9,"substantive_inconsistency"),EXACT(K9,"minor_presentation"),EXACT(K9,"non_inconsistency"),EXACT(K9,"indeterminate")))),AND(AND(D9="retain",E9="protocol_report"),L9&lt;&gt;"",NOT(OR(EXACT(L9,"substantive_difference"),EXACT(L9,"minor_presentation"),EXACT(L9,"version_timing"),EXACT(L9,"non_inconsistency"),EXACT(L9,"indeterminate"))))),"CHECK FIELDS",IF(AND(F9&lt;&gt;"",NOT(OR(EXACT(F9,"no"),EXACT(F9,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F9,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="K9" s="21">
+        <f>IF(AND(OR(D9="retain",D9=""),OR(E9="report_internal_inconsistency",E9="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L9" s="22">
+        <f>IF(AND(OR(D9="retain",D9=""),E9="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M9" s="24" t="n"/>
+      <c r="N9" s="23" t="n"/>
+      <c r="O9" s="23" t="n"/>
+      <c r="P9" s="23" t="n"/>
+      <c r="Q9" s="23" t="n"/>
+      <c r="R9" s="22" t="inlineStr">
+        <is>
+          <t>Table 2 (main p.9) HC vs PT: six cells whose RR CI includes 1 print finite positive NNT intervals, eg 24 (12-186) beside RR 1.13 (0.98-1.30). These six cells, and only these, use an en dash, and eTables 7-8 (Supp4 pp.11, 14) print the same construction with a signed NNH limit, eg 31 (13, -60). Upper limits are NNH values with the minus sign lost; implied NNH from RR limits 152, 70, 59, 39, 68, 84 vs printed 186, 76, 57, 38, 67, 79.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="92" customHeight="1" s="25">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C009</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>NNT point outside its confidence interval</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.9 Table 2 pain intensity 12 months, HC/PT NNT column — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G10" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A10="",COUNTIF($A$2:$A$19,A10)&lt;&gt;1,LEFT(A10,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D10="retain",E10="statistical_results")),H10&lt;&gt;"",NOT(EXACT(H10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="statistical_results")),I10&lt;&gt;"",NOT(EXACT(I10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="statistical_results")),J10&lt;&gt;"",NOT(EXACT(J10,"not_applicable"))),AND(NOT(AND(D10="retain",OR(E10="report_internal_inconsistency",E10="plan_material"))),K10&lt;&gt;"",NOT(EXACT(K10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="protocol_report")),L10&lt;&gt;"",NOT(EXACT(L10,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D10,"retain"),EXACT(D10,"exclude"),EXACT(D10,"discuss"))),NOT(OR(EXACT(E10,"statistical_results"),EXACT(E10,"report_internal_inconsistency"),EXACT(E10,"plan_material"),EXACT(E10,"protocol_report"))),AND(AND(D10="retain",E10="statistical_results"),NOT(OR(EXACT(H10,"confirmed_issue"),EXACT(H10,"probable_issue"),EXACT(H10,"not_issue"),EXACT(H10,"indeterminate")))),AND(AND(D10="retain",E10="statistical_results"),NOT(OR(EXACT(I10,"substantive"),EXACT(I10,"minor_presentation"),EXACT(I10,"indeterminate")))),AND(AND(D10="retain",E10="statistical_results"),J10&lt;&gt;"",NOT(OR(EXACT(J10,"direct"),EXACT(J10,"possible"),EXACT(J10,"unlikely"),EXACT(J10,"unknown")))),AND(AND(D10="retain",OR(E10="report_internal_inconsistency",E10="plan_material")),NOT(OR(EXACT(K10,"substantive_inconsistency"),EXACT(K10,"minor_presentation"),EXACT(K10,"non_inconsistency"),EXACT(K10,"indeterminate")))),AND(AND(D10="retain",E10="protocol_report"),L10&lt;&gt;"",NOT(OR(EXACT(L10,"substantive_difference"),EXACT(L10,"minor_presentation"),EXACT(L10,"version_timing"),EXACT(L10,"non_inconsistency"),EXACT(L10,"indeterminate"))))),"CHECK FIELDS",IF(AND(F10&lt;&gt;"",NOT(OR(EXACT(F10,"no"),EXACT(F10,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F10,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K10" s="21">
+        <f>IF(AND(OR(D10="retain",D10=""),OR(E10="report_internal_inconsistency",E10="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L10" s="22">
+        <f>IF(AND(OR(D10="retain",D10=""),E10="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M10" s="20" t="n"/>
+      <c r="N10" s="23" t="n"/>
+      <c r="O10" s="23" t="n"/>
+      <c r="P10" s="23" t="n"/>
+      <c r="Q10" s="23" t="n"/>
+      <c r="R10" s="22" t="inlineStr">
+        <is>
+          <t>Table 2 (main p.9) intensity 12 mo HC vs PT prints NNT 63 (18-38). Same root cause as C008: RR 1.05 (0.92-1.20) includes 1, so the interval is NNT benefit 18 to infinity to NNH 38 with the minus sign lost (RR-based approximation: NNT 16, NNH 39). Under that reading 63 lies inside; as printed the point is outside its interval.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="92" customHeight="1" s="25">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C010</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>SMD points outside printed confidence intervals</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.10 Table 3 — jama_debar_2025_oi_250046_1755300121.13587.pdf and p.11 PGIC-pain continuation — jama_debar_2025_oi_250046_1755300121.13587.pdf. Every one of the fourteen registered tuples was read directly; all matched the ledger.</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G11" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A11="",COUNTIF($A$2:$A$19,A11)&lt;&gt;1,LEFT(A11,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D11="retain",E11="statistical_results")),H11&lt;&gt;"",NOT(EXACT(H11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="statistical_results")),I11&lt;&gt;"",NOT(EXACT(I11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="statistical_results")),J11&lt;&gt;"",NOT(EXACT(J11,"not_applicable"))),AND(NOT(AND(D11="retain",OR(E11="report_internal_inconsistency",E11="plan_material"))),K11&lt;&gt;"",NOT(EXACT(K11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="protocol_report")),L11&lt;&gt;"",NOT(EXACT(L11,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D11,"retain"),EXACT(D11,"exclude"),EXACT(D11,"discuss"))),NOT(OR(EXACT(E11,"statistical_results"),EXACT(E11,"report_internal_inconsistency"),EXACT(E11,"plan_material"),EXACT(E11,"protocol_report"))),AND(AND(D11="retain",E11="statistical_results"),NOT(OR(EXACT(H11,"confirmed_issue"),EXACT(H11,"probable_issue"),EXACT(H11,"not_issue"),EXACT(H11,"indeterminate")))),AND(AND(D11="retain",E11="statistical_results"),NOT(OR(EXACT(I11,"substantive"),EXACT(I11,"minor_presentation"),EXACT(I11,"indeterminate")))),AND(AND(D11="retain",E11="statistical_results"),J11&lt;&gt;"",NOT(OR(EXACT(J11,"direct"),EXACT(J11,"possible"),EXACT(J11,"unlikely"),EXACT(J11,"unknown")))),AND(AND(D11="retain",OR(E11="report_internal_inconsistency",E11="plan_material")),NOT(OR(EXACT(K11,"substantive_inconsistency"),EXACT(K11,"minor_presentation"),EXACT(K11,"non_inconsistency"),EXACT(K11,"indeterminate")))),AND(AND(D11="retain",E11="protocol_report"),L11&lt;&gt;"",NOT(OR(EXACT(L11,"substantive_difference"),EXACT(L11,"minor_presentation"),EXACT(L11,"version_timing"),EXACT(L11,"non_inconsistency"),EXACT(L11,"indeterminate"))))),"CHECK FIELDS",IF(AND(F11&lt;&gt;"",NOT(OR(EXACT(F11,"no"),EXACT(F11,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F11,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>substantive</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="K11" s="21">
+        <f>IF(AND(OR(D11="retain",D11=""),OR(E11="report_internal_inconsistency",E11="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L11" s="22">
+        <f>IF(AND(OR(D11="retain",D11=""),E11="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M11" s="24" t="n"/>
+      <c r="N11" s="23" t="n"/>
+      <c r="O11" s="23" t="n"/>
+      <c r="P11" s="23" t="n"/>
+      <c r="Q11" s="23" t="n"/>
+      <c r="R11" s="22" t="inlineStr">
+        <is>
+          <t>Table 3 (main pp.10-11): 14 of 63 SMD points lie outside their printed 95% CIs (eg severity 12 mo PT vs UC -0.25 (-0.24 to 0.01)); 18 intervals are printed with descending limits (social, physical rows); in 20 cells the SMD CI and MD CI disagree on excluding zero (eg severity 12 mo PT vs UC MD -0.4 (-0.6 to -0.2) but SMD CI includes 0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="92" customHeight="1" s="25">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C011</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Covariate set of restricted primary analyses</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.4 Adjustment — joi250046supp4_prod_1755300121.15587.pdf, p.7 eTable 2 final imputation/estimation set — joi250046supp4_prod_1755300121.15587.pdf, p.13 Protocol Change Subset Analyses — joi250046supp4_prod_1755300121.15587.pdf, p.14 eTable 8 all three blocks and footnote b — joi250046supp4_prod_1755300121.15587.pdf. Fitted education/employment terms at p.8 — joi250046supp4_prod_1755300121.15587.pdf and p.9 — joi250046supp4_prod_1755300121.15587.pdf were also read as corroboration.</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G12" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A12="",COUNTIF($A$2:$A$19,A12)&lt;&gt;1,LEFT(A12,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D12="retain",E12="statistical_results")),H12&lt;&gt;"",NOT(EXACT(H12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="statistical_results")),I12&lt;&gt;"",NOT(EXACT(I12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="statistical_results")),J12&lt;&gt;"",NOT(EXACT(J12,"not_applicable"))),AND(NOT(AND(D12="retain",OR(E12="report_internal_inconsistency",E12="plan_material"))),K12&lt;&gt;"",NOT(EXACT(K12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="protocol_report")),L12&lt;&gt;"",NOT(EXACT(L12,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D12,"retain"),EXACT(D12,"exclude"),EXACT(D12,"discuss"))),NOT(OR(EXACT(E12,"statistical_results"),EXACT(E12,"report_internal_inconsistency"),EXACT(E12,"plan_material"),EXACT(E12,"protocol_report"))),AND(AND(D12="retain",E12="statistical_results"),NOT(OR(EXACT(H12,"confirmed_issue"),EXACT(H12,"probable_issue"),EXACT(H12,"not_issue"),EXACT(H12,"indeterminate")))),AND(AND(D12="retain",E12="statistical_results"),NOT(OR(EXACT(I12,"substantive"),EXACT(I12,"minor_presentation"),EXACT(I12,"indeterminate")))),AND(AND(D12="retain",E12="statistical_results"),J12&lt;&gt;"",NOT(OR(EXACT(J12,"direct"),EXACT(J12,"possible"),EXACT(J12,"unlikely"),EXACT(J12,"unknown")))),AND(AND(D12="retain",OR(E12="report_internal_inconsistency",E12="plan_material")),NOT(OR(EXACT(K12,"substantive_inconsistency"),EXACT(K12,"minor_presentation"),EXACT(K12,"non_inconsistency"),EXACT(K12,"indeterminate")))),AND(AND(D12="retain",E12="protocol_report"),L12&lt;&gt;"",NOT(OR(EXACT(L12,"substantive_difference"),EXACT(L12,"minor_presentation"),EXACT(L12,"version_timing"),EXACT(L12,"non_inconsistency"),EXACT(L12,"indeterminate"))))),"CHECK FIELDS",IF(AND(F12&lt;&gt;"",NOT(OR(EXACT(F12,"no"),EXACT(F12,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F12,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K12" s="21">
+        <f>IF(AND(OR(D12="retain",D12=""),OR(E12="report_internal_inconsistency",E12="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L12" s="22">
+        <f>IF(AND(OR(D12="retain",D12=""),E12="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="23" t="n"/>
+      <c r="O12" s="23" t="n"/>
+      <c r="P12" s="23" t="n"/>
+      <c r="Q12" s="23" t="n"/>
+      <c r="R12" s="22" t="inlineStr">
+        <is>
+          <t>Supp4 p.13 describes eTable 8 as the primary analysis restricted to subsets, but eTable 8 footnote b (p.14) lists only the base covariates (sex, age, site, residence, multisite pain, mental health, baseline severity), omitting the education and employment terms that eTable 2 (p.7) adds to the primary models. The footnote is identical to eTable 7's complete-case footnote. Report contradicts itself on the subset model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="92" customHeight="1" s="25">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C012</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Final response-weight model predictor membership</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.4 Adjustment/selection — joi250046supp4_prod_1755300121.15587.pdf, p.5 Non-Response Weighting — joi250046supp4_prod_1755300121.15587.pdf, p.7 eTable 2 final nonresponse predictors — joi250046supp4_prod_1755300121.15587.pdf, p.10 eTable 5 full coefficient display — joi250046supp4_prod_1755300121.15587.pdf; corroborating REPORT workbook — joi250046supp5_prod_1755300121.16087.xlsx, worksheet eTable 3, cells A18, H18, I18, J18.</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G13" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A13="",COUNTIF($A$2:$A$19,A13)&lt;&gt;1,LEFT(A13,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D13="retain",E13="statistical_results")),H13&lt;&gt;"",NOT(EXACT(H13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="statistical_results")),I13&lt;&gt;"",NOT(EXACT(I13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="statistical_results")),J13&lt;&gt;"",NOT(EXACT(J13,"not_applicable"))),AND(NOT(AND(D13="retain",OR(E13="report_internal_inconsistency",E13="plan_material"))),K13&lt;&gt;"",NOT(EXACT(K13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="protocol_report")),L13&lt;&gt;"",NOT(EXACT(L13,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D13,"retain"),EXACT(D13,"exclude"),EXACT(D13,"discuss"))),NOT(OR(EXACT(E13,"statistical_results"),EXACT(E13,"report_internal_inconsistency"),EXACT(E13,"plan_material"),EXACT(E13,"protocol_report"))),AND(AND(D13="retain",E13="statistical_results"),NOT(OR(EXACT(H13,"confirmed_issue"),EXACT(H13,"probable_issue"),EXACT(H13,"not_issue"),EXACT(H13,"indeterminate")))),AND(AND(D13="retain",E13="statistical_results"),NOT(OR(EXACT(I13,"substantive"),EXACT(I13,"minor_presentation"),EXACT(I13,"indeterminate")))),AND(AND(D13="retain",E13="statistical_results"),J13&lt;&gt;"",NOT(OR(EXACT(J13,"direct"),EXACT(J13,"possible"),EXACT(J13,"unlikely"),EXACT(J13,"unknown")))),AND(AND(D13="retain",OR(E13="report_internal_inconsistency",E13="plan_material")),NOT(OR(EXACT(K13,"substantive_inconsistency"),EXACT(K13,"minor_presentation"),EXACT(K13,"non_inconsistency"),EXACT(K13,"indeterminate")))),AND(AND(D13="retain",E13="protocol_report"),L13&lt;&gt;"",NOT(OR(EXACT(L13,"substantive_difference"),EXACT(L13,"minor_presentation"),EXACT(L13,"version_timing"),EXACT(L13,"non_inconsistency"),EXACT(L13,"indeterminate"))))),"CHECK FIELDS",IF(AND(F13&lt;&gt;"",NOT(OR(EXACT(F13,"no"),EXACT(F13,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F13,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K13" s="21">
+        <f>IF(AND(OR(D13="retain",D13=""),OR(E13="report_internal_inconsistency",E13="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L13" s="22">
+        <f>IF(AND(OR(D13="retain",D13=""),E13="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M13" s="24" t="n"/>
+      <c r="N13" s="23" t="n"/>
+      <c r="O13" s="23" t="n"/>
+      <c r="P13" s="23" t="n"/>
+      <c r="Q13" s="23" t="n"/>
+      <c r="R13" s="22" t="inlineStr">
+        <is>
+          <t>eTable 2 (Supp4 p.7) lists education among the additional nonresponse-weight predictors; the fitted weight model, eTable 5 (p.10), has no education term but includes 'Not employed'. Workbook (Supp5 eTable 3) selection P values support employment (MCID P&lt;.001, nonresponse P=.0228) and not education (no nonresponse P listed), so eTable 2's list appears wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="92" customHeight="1" s="25">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C013</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Education coding and coefficient attribution</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.7 eTable 2 final primary predictor list — joi250046supp4_prod_1755300121.15587.pdf, p.8 eTable 3 all three education rows — joi250046supp4_prod_1755300121.15587.pdf, p.9 eTable 4 all three education rows — joi250046supp4_prod_1755300121.15587.pdf; corroborating REPORT workbook — joi250046supp5_prod_1755300121.16087.xlsx, worksheet eTable 3, cells A12:A16.</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G14" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A14="",COUNTIF($A$2:$A$19,A14)&lt;&gt;1,LEFT(A14,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D14="retain",E14="statistical_results")),H14&lt;&gt;"",NOT(EXACT(H14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="statistical_results")),I14&lt;&gt;"",NOT(EXACT(I14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="statistical_results")),J14&lt;&gt;"",NOT(EXACT(J14,"not_applicable"))),AND(NOT(AND(D14="retain",OR(E14="report_internal_inconsistency",E14="plan_material"))),K14&lt;&gt;"",NOT(EXACT(K14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="protocol_report")),L14&lt;&gt;"",NOT(EXACT(L14,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D14,"retain"),EXACT(D14,"exclude"),EXACT(D14,"discuss"))),NOT(OR(EXACT(E14,"statistical_results"),EXACT(E14,"report_internal_inconsistency"),EXACT(E14,"plan_material"),EXACT(E14,"protocol_report"))),AND(AND(D14="retain",E14="statistical_results"),NOT(OR(EXACT(H14,"confirmed_issue"),EXACT(H14,"probable_issue"),EXACT(H14,"not_issue"),EXACT(H14,"indeterminate")))),AND(AND(D14="retain",E14="statistical_results"),NOT(OR(EXACT(I14,"substantive"),EXACT(I14,"minor_presentation"),EXACT(I14,"indeterminate")))),AND(AND(D14="retain",E14="statistical_results"),J14&lt;&gt;"",NOT(OR(EXACT(J14,"direct"),EXACT(J14,"possible"),EXACT(J14,"unlikely"),EXACT(J14,"unknown")))),AND(AND(D14="retain",OR(E14="report_internal_inconsistency",E14="plan_material")),NOT(OR(EXACT(K14,"substantive_inconsistency"),EXACT(K14,"minor_presentation"),EXACT(K14,"non_inconsistency"),EXACT(K14,"indeterminate")))),AND(AND(D14="retain",E14="protocol_report"),L14&lt;&gt;"",NOT(OR(EXACT(L14,"substantive_difference"),EXACT(L14,"minor_presentation"),EXACT(L14,"version_timing"),EXACT(L14,"non_inconsistency"),EXACT(L14,"indeterminate"))))),"CHECK FIELDS",IF(AND(F14&lt;&gt;"",NOT(OR(EXACT(F14,"no"),EXACT(F14,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F14,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K14" s="21">
+        <f>IF(AND(OR(D14="retain",D14=""),OR(E14="report_internal_inconsistency",E14="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L14" s="22">
+        <f>IF(AND(OR(D14="retain",D14=""),E14="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M14" s="20" t="n"/>
+      <c r="N14" s="23" t="n"/>
+      <c r="O14" s="23" t="n"/>
+      <c r="P14" s="23" t="n"/>
+      <c r="Q14" s="23" t="n"/>
+      <c r="R14" s="22" t="inlineStr">
+        <is>
+          <t>eTable 2 (Supp4 p.7) specifies education as binary (any college vs HS or less), but eTables 3 and 4 (pp.8-9) fit three nonreference education terms, two of them labeled 'AA degree' (eg eTable 4 RR 0.97 and 1.16). The workbook (Supp5) has four education levels (HS or less, Associate's/technical, College, Doctoral/postgraduate), consistent with a 4-level coding and a duplicated label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="92" customHeight="1" s="25">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C014</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Coefficient CI versus P-value null-significance pattern</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.8 eTable 3 seven registered rows — joi250046supp4_prod_1755300121.15587.pdf, p.9 eTable 4 age and second AA rows — joi250046supp4_prod_1755300121.15587.pdf, p.10 eTable 5 PEG row — joi250046supp4_prod_1755300121.15587.pdf. Method context was read at results p.4 — joi250046supp4_prod_1755300121.15587.pdf, p.5 — joi250046supp4_prod_1755300121.15587.pdf, and REPORT main p.4 two-sided alpha=.05 — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G15" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A15="",COUNTIF($A$2:$A$19,A15)&lt;&gt;1,LEFT(A15,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D15="retain",E15="statistical_results")),H15&lt;&gt;"",NOT(EXACT(H15,"not_applicable"))),AND(NOT(AND(D15="retain",E15="statistical_results")),I15&lt;&gt;"",NOT(EXACT(I15,"not_applicable"))),AND(NOT(AND(D15="retain",E15="statistical_results")),J15&lt;&gt;"",NOT(EXACT(J15,"not_applicable"))),AND(NOT(AND(D15="retain",OR(E15="report_internal_inconsistency",E15="plan_material"))),K15&lt;&gt;"",NOT(EXACT(K15,"not_applicable"))),AND(NOT(AND(D15="retain",E15="protocol_report")),L15&lt;&gt;"",NOT(EXACT(L15,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D15,"retain"),EXACT(D15,"exclude"),EXACT(D15,"discuss"))),NOT(OR(EXACT(E15,"statistical_results"),EXACT(E15,"report_internal_inconsistency"),EXACT(E15,"plan_material"),EXACT(E15,"protocol_report"))),AND(AND(D15="retain",E15="statistical_results"),NOT(OR(EXACT(H15,"confirmed_issue"),EXACT(H15,"probable_issue"),EXACT(H15,"not_issue"),EXACT(H15,"indeterminate")))),AND(AND(D15="retain",E15="statistical_results"),NOT(OR(EXACT(I15,"substantive"),EXACT(I15,"minor_presentation"),EXACT(I15,"indeterminate")))),AND(AND(D15="retain",E15="statistical_results"),J15&lt;&gt;"",NOT(OR(EXACT(J15,"direct"),EXACT(J15,"possible"),EXACT(J15,"unlikely"),EXACT(J15,"unknown")))),AND(AND(D15="retain",OR(E15="report_internal_inconsistency",E15="plan_material")),NOT(OR(EXACT(K15,"substantive_inconsistency"),EXACT(K15,"minor_presentation"),EXACT(K15,"non_inconsistency"),EXACT(K15,"indeterminate")))),AND(AND(D15="retain",E15="protocol_report"),L15&lt;&gt;"",NOT(OR(EXACT(L15,"substantive_difference"),EXACT(L15,"minor_presentation"),EXACT(L15,"version_timing"),EXACT(L15,"non_inconsistency"),EXACT(L15,"indeterminate"))))),"CHECK FIELDS",IF(AND(F15&lt;&gt;"",NOT(OR(EXACT(F15,"no"),EXACT(F15,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F15,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K15" s="21">
+        <f>IF(AND(OR(D15="retain",D15=""),OR(E15="report_internal_inconsistency",E15="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L15" s="22">
+        <f>IF(AND(OR(D15="retain",D15=""),E15="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M15" s="24" t="n"/>
+      <c r="N15" s="23" t="n"/>
+      <c r="O15" s="23" t="n"/>
+      <c r="P15" s="23" t="n"/>
+      <c r="Q15" s="23" t="n"/>
+      <c r="R15" s="22" t="inlineStr">
+        <is>
+          <t>eTable 3 (Supp4 p.8): 7 rows have 95% CIs excluding 0 but P&gt;.05 (eg Pattern 2 -0.28 (-0.47 to -0.08), P=.150). Printed P values reproduce almost exactly if each interval is estimate +/- 1 SE (r = 0.999 over rows with P&gt;=.001; SE implied by P is 1.95 x the 95%-CI SE), so the 'CIs' are ~68% intervals. The three ratio rows in eTables 4-5 (age, second AA, PEG) are compatible with rounding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="92" customHeight="1" s="25">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C015</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Within-header three-month subset counts</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.14 eTable 8 first subgroup header — joi250046supp4_prod_1755300121.15587.pdf; corroborating REPORT p.7 eTable 1 — joi250046supp4_prod_1755300121.15587.pdf, p.13 subset definition — joi250046supp4_prod_1755300121.15587.pdf, and the second/third headers on p.14.</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G16" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A16="",COUNTIF($A$2:$A$19,A16)&lt;&gt;1,LEFT(A16,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D16="retain",E16="statistical_results")),H16&lt;&gt;"",NOT(EXACT(H16,"not_applicable"))),AND(NOT(AND(D16="retain",E16="statistical_results")),I16&lt;&gt;"",NOT(EXACT(I16,"not_applicable"))),AND(NOT(AND(D16="retain",E16="statistical_results")),J16&lt;&gt;"",NOT(EXACT(J16,"not_applicable"))),AND(NOT(AND(D16="retain",OR(E16="report_internal_inconsistency",E16="plan_material"))),K16&lt;&gt;"",NOT(EXACT(K16,"not_applicable"))),AND(NOT(AND(D16="retain",E16="protocol_report")),L16&lt;&gt;"",NOT(EXACT(L16,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D16,"retain"),EXACT(D16,"exclude"),EXACT(D16,"discuss"))),NOT(OR(EXACT(E16,"statistical_results"),EXACT(E16,"report_internal_inconsistency"),EXACT(E16,"plan_material"),EXACT(E16,"protocol_report"))),AND(AND(D16="retain",E16="statistical_results"),NOT(OR(EXACT(H16,"confirmed_issue"),EXACT(H16,"probable_issue"),EXACT(H16,"not_issue"),EXACT(H16,"indeterminate")))),AND(AND(D16="retain",E16="statistical_results"),NOT(OR(EXACT(I16,"substantive"),EXACT(I16,"minor_presentation"),EXACT(I16,"indeterminate")))),AND(AND(D16="retain",E16="statistical_results"),J16&lt;&gt;"",NOT(OR(EXACT(J16,"direct"),EXACT(J16,"possible"),EXACT(J16,"unlikely"),EXACT(J16,"unknown")))),AND(AND(D16="retain",OR(E16="report_internal_inconsistency",E16="plan_material")),NOT(OR(EXACT(K16,"substantive_inconsistency"),EXACT(K16,"minor_presentation"),EXACT(K16,"non_inconsistency"),EXACT(K16,"indeterminate")))),AND(AND(D16="retain",E16="protocol_report"),L16&lt;&gt;"",NOT(OR(EXACT(L16,"substantive_difference"),EXACT(L16,"minor_presentation"),EXACT(L16,"version_timing"),EXACT(L16,"non_inconsistency"),EXACT(L16,"indeterminate"))))),"CHECK FIELDS",IF(AND(F16&lt;&gt;"",NOT(OR(EXACT(F16,"no"),EXACT(F16,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F16,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K16" s="21">
+        <f>IF(AND(OR(D16="retain",D16=""),OR(E16="report_internal_inconsistency",E16="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L16" s="22">
+        <f>IF(AND(OR(D16="retain",D16=""),E16="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M16" s="20" t="n"/>
+      <c r="N16" s="23" t="n"/>
+      <c r="O16" s="23" t="n"/>
+      <c r="P16" s="23" t="n"/>
+      <c r="Q16" s="23" t="n"/>
+      <c r="R16" s="22" t="inlineStr">
+        <is>
+          <t>eTable 8 first header (Supp4 p.14): 'N=454; 366 with at least 1 follow-up; PT=149, HC=153, UC=152 at 3-months'. 149+153+152 = 454 = N randomized, which exceeds the 366 with any follow-up, so these are not 3-month counts. By subtraction (eTable 1 minus the post-8/9/2021 header) the 3-month counts would be UC 109, PT 94, HC 108 (total 311).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="92" customHeight="1" s="25">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C016</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Raw-score summary statistic and bounds in eTable 11</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.15 Additional Unadjusted Data and Analyses — joi250046supp4_prod_1755300121.15587.pdf, p.17 eTable 11 title/header and all 21 rows — joi250046supp4_prod_1755300121.15587.pdf, p.18 note b — joi250046supp4_prod_1755300121.15587.pdf; corroborating REPORT main p.11 PGIC footnotes h/i — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G17" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A17="",COUNTIF($A$2:$A$19,A17)&lt;&gt;1,LEFT(A17,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D17="retain",E17="statistical_results")),H17&lt;&gt;"",NOT(EXACT(H17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="statistical_results")),I17&lt;&gt;"",NOT(EXACT(I17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="statistical_results")),J17&lt;&gt;"",NOT(EXACT(J17,"not_applicable"))),AND(NOT(AND(D17="retain",OR(E17="report_internal_inconsistency",E17="plan_material"))),K17&lt;&gt;"",NOT(EXACT(K17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="protocol_report")),L17&lt;&gt;"",NOT(EXACT(L17,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D17,"retain"),EXACT(D17,"exclude"),EXACT(D17,"discuss"))),NOT(OR(EXACT(E17,"statistical_results"),EXACT(E17,"report_internal_inconsistency"),EXACT(E17,"plan_material"),EXACT(E17,"protocol_report"))),AND(AND(D17="retain",E17="statistical_results"),NOT(OR(EXACT(H17,"confirmed_issue"),EXACT(H17,"probable_issue"),EXACT(H17,"not_issue"),EXACT(H17,"indeterminate")))),AND(AND(D17="retain",E17="statistical_results"),NOT(OR(EXACT(I17,"substantive"),EXACT(I17,"minor_presentation"),EXACT(I17,"indeterminate")))),AND(AND(D17="retain",E17="statistical_results"),J17&lt;&gt;"",NOT(OR(EXACT(J17,"direct"),EXACT(J17,"possible"),EXACT(J17,"unlikely"),EXACT(J17,"unknown")))),AND(AND(D17="retain",OR(E17="report_internal_inconsistency",E17="plan_material")),NOT(OR(EXACT(K17,"substantive_inconsistency"),EXACT(K17,"minor_presentation"),EXACT(K17,"non_inconsistency"),EXACT(K17,"indeterminate")))),AND(AND(D17="retain",E17="protocol_report"),L17&lt;&gt;"",NOT(OR(EXACT(L17,"substantive_difference"),EXACT(L17,"minor_presentation"),EXACT(L17,"version_timing"),EXACT(L17,"non_inconsistency"),EXACT(L17,"indeterminate"))))),"CHECK FIELDS",IF(AND(F17&lt;&gt;"",NOT(OR(EXACT(F17,"no"),EXACT(F17,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F17,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>substantive</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="K17" s="21">
+        <f>IF(AND(OR(D17="retain",D17=""),OR(E17="report_internal_inconsistency",E17="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L17" s="22">
+        <f>IF(AND(OR(D17="retain",D17=""),E17="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M17" s="24" t="n"/>
+      <c r="N17" s="23" t="n"/>
+      <c r="O17" s="23" t="n"/>
+      <c r="P17" s="23" t="n"/>
+      <c r="Q17" s="23" t="n"/>
+      <c r="R17" s="22" t="inlineStr">
+        <is>
+          <t>eTable 11 (Supp4 p.17) is titled and headed 'Raw Score Median (25%-tile, 75%-tile)' but the text (p.15) calls the values means; bounds such as 5.1 (4.9, 5.2) for a 0-10 score (baseline SD 1.6) are far too narrow for IQRs and look like 95% CIs of means. Group columns also appear to be in the order UC, PT, HC, not the labeled PT, HC, UC: printed MDs match differences under UC/PT/HC (mean abs error 0.03) but not as labeled (1.02).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="92" customHeight="1" s="25">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C017</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Workbook All Observed depression percentage</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Yes: supplied REPORT workbook — joi250046supp5_prod_1755300121.16087.xlsx, worksheet exactly eTable 3, E3, A82, E82, A83, E83, A110. Direct workbook.xml confirms worksheet name and worksheet relationship; direct sheet1.xml/sharedStrings.xml confirms all cells. B82/C82/D82 were also read as count-partition corroboration.</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G18" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A18="",COUNTIF($A$2:$A$19,A18)&lt;&gt;1,LEFT(A18,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D18="retain",E18="statistical_results")),H18&lt;&gt;"",NOT(EXACT(H18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="statistical_results")),I18&lt;&gt;"",NOT(EXACT(I18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="statistical_results")),J18&lt;&gt;"",NOT(EXACT(J18,"not_applicable"))),AND(NOT(AND(D18="retain",OR(E18="report_internal_inconsistency",E18="plan_material"))),K18&lt;&gt;"",NOT(EXACT(K18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="protocol_report")),L18&lt;&gt;"",NOT(EXACT(L18,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D18,"retain"),EXACT(D18,"exclude"),EXACT(D18,"discuss"))),NOT(OR(EXACT(E18,"statistical_results"),EXACT(E18,"report_internal_inconsistency"),EXACT(E18,"plan_material"),EXACT(E18,"protocol_report"))),AND(AND(D18="retain",E18="statistical_results"),NOT(OR(EXACT(H18,"confirmed_issue"),EXACT(H18,"probable_issue"),EXACT(H18,"not_issue"),EXACT(H18,"indeterminate")))),AND(AND(D18="retain",E18="statistical_results"),NOT(OR(EXACT(I18,"substantive"),EXACT(I18,"minor_presentation"),EXACT(I18,"indeterminate")))),AND(AND(D18="retain",E18="statistical_results"),J18&lt;&gt;"",NOT(OR(EXACT(J18,"direct"),EXACT(J18,"possible"),EXACT(J18,"unlikely"),EXACT(J18,"unknown")))),AND(AND(D18="retain",OR(E18="report_internal_inconsistency",E18="plan_material")),NOT(OR(EXACT(K18,"substantive_inconsistency"),EXACT(K18,"minor_presentation"),EXACT(K18,"non_inconsistency"),EXACT(K18,"indeterminate")))),AND(AND(D18="retain",E18="protocol_report"),L18&lt;&gt;"",NOT(OR(EXACT(L18,"substantive_difference"),EXACT(L18,"minor_presentation"),EXACT(L18,"version_timing"),EXACT(L18,"non_inconsistency"),EXACT(L18,"indeterminate"))))),"CHECK FIELDS",IF(AND(F18&lt;&gt;"",NOT(OR(EXACT(F18,"no"),EXACT(F18,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F18,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K18" s="21">
+        <f>IF(AND(OR(D18="retain",D18=""),OR(E18="report_internal_inconsistency",E18="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L18" s="22">
+        <f>IF(AND(OR(D18="retain",D18=""),E18="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M18" s="20" t="n"/>
+      <c r="N18" s="23" t="n"/>
+      <c r="O18" s="23" t="n"/>
+      <c r="P18" s="23" t="n"/>
+      <c r="Q18" s="23" t="n"/>
+      <c r="R18" s="22" t="inlineStr">
+        <is>
+          <t>Supp5 workbook, sheet 'eTable 3', E82: All Observed (N=1568, 2 missing per E83) current depression '711 (73.2)'. 711/1566 = 45.4%. Row reconciles otherwise: 162+243+711 = 1116 (B82), and B82 1116/2329 = 47.9%, C82 162/295 = 54.9%, D82 243/468 = 51.9% reproduce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="92" customHeight="1" s="25">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C018</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>Physical-function omnibus P values and contrast intervals</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>Results supplement PDF p17, eTable 11 Physical Functioning 6 months — joi250046supp4_prod_1755300121.15587.pdf (REPORT); Results supplement PDF p17, eTable 11 Physical Functioning 12 months — joi250046supp4_prod_1755300121.15587.pdf (REPORT); Results supplement PDF p17, all other 19 eTable 11 outcome/time rows — joi250046supp4_prod_1755300121.15587.pdf (REPORT, same-display corroboration); Results supplement PDF p18, eTable 11 note b — joi250046supp4_prod_1755300121.15587.pdf (REPORT); Results supplement PDF page 15, Additional Unadjusted Data and Analyses — joi250046supp4_prod_1755300121.15587.pdf (REPORT); Main article PDF p11, Table 3 note c — jama_debar_2025_oi_250046_1755300121.13587.pdf (REPORT, corroboration only); Main article PDF p4, Statistical Analysis — jama_debar_2025_oi_250046_1755300121.13587.pdf (REPORT, corroboration only); The rendered p17 heading is unadjusted between-group mean differences (95%CI), with PT vs UC, HC vs UC and HC vs PT columns and a separately named omnibus P column. No pairwise P value is printed. The comparison does not equate raw medians with fitted means, and does not equate a single pairwise null with the omnibus null</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G19" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A19="",COUNTIF($A$2:$A$19,A19)&lt;&gt;1,LEFT(A19,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D19="retain",E19="statistical_results")),H19&lt;&gt;"",NOT(EXACT(H19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="statistical_results")),I19&lt;&gt;"",NOT(EXACT(I19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="statistical_results")),J19&lt;&gt;"",NOT(EXACT(J19,"not_applicable"))),AND(NOT(AND(D19="retain",OR(E19="report_internal_inconsistency",E19="plan_material"))),K19&lt;&gt;"",NOT(EXACT(K19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="protocol_report")),L19&lt;&gt;"",NOT(EXACT(L19,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D19,"retain"),EXACT(D19,"exclude"),EXACT(D19,"discuss"))),NOT(OR(EXACT(E19,"statistical_results"),EXACT(E19,"report_internal_inconsistency"),EXACT(E19,"plan_material"),EXACT(E19,"protocol_report"))),AND(AND(D19="retain",E19="statistical_results"),NOT(OR(EXACT(H19,"confirmed_issue"),EXACT(H19,"probable_issue"),EXACT(H19,"not_issue"),EXACT(H19,"indeterminate")))),AND(AND(D19="retain",E19="statistical_results"),NOT(OR(EXACT(I19,"substantive"),EXACT(I19,"minor_presentation"),EXACT(I19,"indeterminate")))),AND(AND(D19="retain",E19="statistical_results"),J19&lt;&gt;"",NOT(OR(EXACT(J19,"direct"),EXACT(J19,"possible"),EXACT(J19,"unlikely"),EXACT(J19,"unknown")))),AND(AND(D19="retain",OR(E19="report_internal_inconsistency",E19="plan_material")),NOT(OR(EXACT(K19,"substantive_inconsistency"),EXACT(K19,"minor_presentation"),EXACT(K19,"non_inconsistency"),EXACT(K19,"indeterminate")))),AND(AND(D19="retain",E19="protocol_report"),L19&lt;&gt;"",NOT(OR(EXACT(L19,"substantive_difference"),EXACT(L19,"minor_presentation"),EXACT(L19,"version_timing"),EXACT(L19,"non_inconsistency"),EXACT(L19,"indeterminate"))))),"CHECK FIELDS",IF(AND(F19&lt;&gt;"",NOT(OR(EXACT(F19,"no"),EXACT(F19,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F19,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>probable_issue</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K19" s="21">
+        <f>IF(AND(OR(D19="retain",D19=""),OR(E19="report_internal_inconsistency",E19="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L19" s="22">
+        <f>IF(AND(OR(D19="retain",D19=""),E19="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M19" s="24" t="n"/>
+      <c r="N19" s="23" t="n"/>
+      <c r="O19" s="23" t="n"/>
+      <c r="P19" s="23" t="n"/>
+      <c r="Q19" s="23" t="n"/>
+      <c r="R19" s="22" t="inlineStr">
+        <is>
+          <t>eTable 11 (Supp4 p.17) physical function: 2-df Wald omnibus P reconstructed from the three contrast CIs (Cov from Var(HC-PT) = Var(a)+Var(b)-2Cov) is .025 at 6 mo and .010 at 12 mo, vs printed .005 and .001; P ranges allowing +/-0.05 display rounding are .0096-.051 and .0032-.024, excluding the printed values. The other rows are compatible. Probable because eTable 11 does not define its omnibus test.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R19"/>
+  <conditionalFormatting sqref="H2:H19">
+    <cfRule type="expression" priority="8" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I19">
+    <cfRule type="expression" priority="9" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J19">
+    <cfRule type="expression" priority="10" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K19">
+    <cfRule type="expression" priority="11" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),OR($E2="report_internal_inconsistency",$E2="plan_material")))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L19">
+    <cfRule type="expression" priority="12" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="protocol_report"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G19">
+    <cfRule type="expression" priority="13" dxfId="71">
+      <formula>G2&lt;&gt;"PRIMARY READY"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="8">
+    <dataValidation sqref="D2:D19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"retain,exclude,discuss"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"statistical_results,report_internal_inconsistency,plan_material,protocol_report"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"no,primary_done"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"confirmed_issue,probable_issue,not_issue,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive,minor_presentation,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"direct,possible,unlikely,unknown,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive_inconsistency,minor_presentation,non_inconsistency,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive_difference,minor_presentation,version_timing,non_inconsistency,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11644,7 +12909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="14" min="1" max="1"/>
@@ -11739,15 +13004,470 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="26" t="inlineStr">
-        <is>
-          <t>Placeholder: no workflow 1.6.2 output for this paper yet; nothing to review in v.2.4.1.</t>
+    <row r="2" ht="92" customHeight="1" s="25">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C001</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>PROMIS-29 scalar scoring and direction are not specified</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 3, Secondary Outcomes: domain definition and direction; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, Secondary Outcomes: single scalar result; joi250066supp3_prod_1761597796.4701.pdf — p. 15, eTable 4, PROMIS 29 row: corroborating scalar and adjusted result; joi250066supp1_prod_1761597796.4601.pdf — p. 70, PROMIS assessment: contextual scale description</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G2" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A2="",COUNTIF($A$2:$A$7,A2)&lt;&gt;1,LEFT(A2,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D2="retain",E2="statistical_results")),H2&lt;&gt;"",NOT(EXACT(H2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),I2&lt;&gt;"",NOT(EXACT(I2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),J2&lt;&gt;"",NOT(EXACT(J2,"not_applicable"))),AND(NOT(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material"))),K2&lt;&gt;"",NOT(EXACT(K2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="protocol_report")),L2&lt;&gt;"",NOT(EXACT(L2,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D2,"retain"),EXACT(D2,"exclude"),EXACT(D2,"discuss"))),NOT(OR(EXACT(E2,"statistical_results"),EXACT(E2,"report_internal_inconsistency"),EXACT(E2,"plan_material"),EXACT(E2,"protocol_report"))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(H2,"confirmed_issue"),EXACT(H2,"probable_issue"),EXACT(H2,"not_issue"),EXACT(H2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(I2,"substantive"),EXACT(I2,"minor_presentation"),EXACT(I2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),J2&lt;&gt;"",NOT(OR(EXACT(J2,"direct"),EXACT(J2,"possible"),EXACT(J2,"unlikely"),EXACT(J2,"unknown")))),AND(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material")),NOT(OR(EXACT(K2,"substantive_inconsistency"),EXACT(K2,"minor_presentation"),EXACT(K2,"non_inconsistency"),EXACT(K2,"indeterminate")))),AND(AND(D2="retain",E2="protocol_report"),L2&lt;&gt;"",NOT(OR(EXACT(L2,"substantive_difference"),EXACT(L2,"minor_presentation"),EXACT(L2,"version_timing"),EXACT(L2,"non_inconsistency"),EXACT(L2,"indeterminate"))))),"CHECK FIELDS",IF(AND(F2&lt;&gt;"",NOT(OR(EXACT(F2,"no"),EXACT(F2,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F2,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H2" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I2" s="21" t="inlineStr">
+        <is>
+          <t>substantive</t>
+        </is>
+      </c>
+      <c r="J2" s="22" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="K2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),OR(E2="report_internal_inconsistency",E2="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L2" s="22">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M2" s="20" t="n"/>
+      <c r="N2" s="23" t="n"/>
+      <c r="O2" s="23" t="n"/>
+      <c r="P2" s="23" t="n"/>
+      <c r="Q2" s="23" t="n"/>
+      <c r="R2" s="22" t="inlineStr">
+        <is>
+          <t>Main p.3 describes PROMIS-29 as 7 domains (raw 4-20 each) of mixed direction, yet p.6 and eTable 4 (Supp3 p.15) report one 'PROMIS-29 score' (about 65, SD 14) and an adjusted MD of -0.37 (-3.34 to 2.61) with no aggregation, transformation or favorable direction stated; protocol p.70 describes domain T-scores (mean 50, SD 10). Also main p.6 levodopa mean 66 vs eTable 4 64.74.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="92" customHeight="1" s="25">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C002</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Primary analysis population changes from all randomized participants to survivors</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>joi250066supp1_prod_1761597796.4601.pdf — p. 86, §§11.4.1–11.4.2: FAS and primary assignment; joi250066supp1_prod_1761597796.4601.pdf — p. 87, §11.5: missing-data rule; joi250066supp2_prod_1761597796.4701.pdf — p. 4, §3.2 and footnote: deceased participants' contribution; joi250066supp2_prod_1761597796.4701.pdf — p. 6, §4.3: primary/supportive status; joi250066supp2_prod_1761597796.4701.pdf — p. 7, §§4.3.1–4.3.3: primary versus death-inclusive strategy; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 4, Statistical Analyses: survivor-primary rule; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 5, flow and SAP explanation: participant totals and timing; joi250066supp3_prod_1761597796.4701.pdf — p. 12, population definitions: primary death exclusion; joi250066supp3_prod_1761597796.4701.pdf — p. 13, eTable 2, estimands 1, 3 and 4: primary and death-inclusive results</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G3" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A3="",COUNTIF($A$2:$A$7,A3)&lt;&gt;1,LEFT(A3,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D3="retain",E3="statistical_results")),H3&lt;&gt;"",NOT(EXACT(H3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),I3&lt;&gt;"",NOT(EXACT(I3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),J3&lt;&gt;"",NOT(EXACT(J3,"not_applicable"))),AND(NOT(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material"))),K3&lt;&gt;"",NOT(EXACT(K3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="protocol_report")),L3&lt;&gt;"",NOT(EXACT(L3,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D3,"retain"),EXACT(D3,"exclude"),EXACT(D3,"discuss"))),NOT(OR(EXACT(E3,"statistical_results"),EXACT(E3,"report_internal_inconsistency"),EXACT(E3,"plan_material"),EXACT(E3,"protocol_report"))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(H3,"confirmed_issue"),EXACT(H3,"probable_issue"),EXACT(H3,"not_issue"),EXACT(H3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(I3,"substantive"),EXACT(I3,"minor_presentation"),EXACT(I3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),J3&lt;&gt;"",NOT(OR(EXACT(J3,"direct"),EXACT(J3,"possible"),EXACT(J3,"unlikely"),EXACT(J3,"unknown")))),AND(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material")),NOT(OR(EXACT(K3,"substantive_inconsistency"),EXACT(K3,"minor_presentation"),EXACT(K3,"non_inconsistency"),EXACT(K3,"indeterminate")))),AND(AND(D3="retain",E3="protocol_report"),L3&lt;&gt;"",NOT(OR(EXACT(L3,"substantive_difference"),EXACT(L3,"minor_presentation"),EXACT(L3,"version_timing"),EXACT(L3,"non_inconsistency"),EXACT(L3,"indeterminate"))))),"CHECK FIELDS",IF(AND(F3&lt;&gt;"",NOT(OR(EXACT(F3,"no"),EXACT(F3,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F3,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J3" s="22">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),OR(E3="report_internal_inconsistency",E3="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L3" s="22" t="inlineStr">
+        <is>
+          <t>substantive_difference</t>
+        </is>
+      </c>
+      <c r="M3" s="24" t="n"/>
+      <c r="N3" s="23" t="n"/>
+      <c r="O3" s="23" t="n"/>
+      <c r="P3" s="23" t="n"/>
+      <c r="Q3" s="23" t="n"/>
+      <c r="R3" s="22" t="inlineStr">
+        <is>
+          <t>Protocol §11.4.1-11.4.2 (p.86) and §11.5 (p.87): primary analysis in the FAS of all randomized, missing data by multiple imputation. SAP (p.4 footnote 1; §4.3) and report (main p.4; Supp3 pp.12-13) exclude the 28 participants who died before 3 months from the primary analysis (n=582 of 610); death-inclusive analyses (estimands 3, 4; post hoc estimand 10) are supportive. Report calls the protocol-SAP differences 'terminology' (main p.5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="92" customHeight="1" s="25">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C003</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Primary mixed-model terms are absent from the implemented linear model</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>joi250066supp1_prod_1761597796.4601.pdf — p. 56, statistical synopsis: final mixed-model summary; joi250066supp1_prod_1761597796.4601.pdf — p. 86, §11.4.2: final primary formula/variance structure; joi250066supp2_prod_1761597796.4701.pdf — p. 10, §5.2: baseline/treatment linear model; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 4, Statistical Analyses: reported model; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 5, alignment explanation: SAP timing and alignment context; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, Primary Outcome: affected primary result; joi250066supp5_prod_1761597796.4751.pdf — p. 1, code lines 19–26 and 31–32: explicit implementation and pooling; joi250066supp1_prod_1761597796.4601.pdf — p. 10, earlier synopsis: historical center-term context; joi250066supp1_prod_1761597796.4601.pdf — p. 39, earlier §11.4.2: historical center-term context</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G4" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A4="",COUNTIF($A$2:$A$7,A4)&lt;&gt;1,LEFT(A4,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D4="retain",E4="statistical_results")),H4&lt;&gt;"",NOT(EXACT(H4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),I4&lt;&gt;"",NOT(EXACT(I4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),J4&lt;&gt;"",NOT(EXACT(J4,"not_applicable"))),AND(NOT(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material"))),K4&lt;&gt;"",NOT(EXACT(K4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="protocol_report")),L4&lt;&gt;"",NOT(EXACT(L4,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D4,"retain"),EXACT(D4,"exclude"),EXACT(D4,"discuss"))),NOT(OR(EXACT(E4,"statistical_results"),EXACT(E4,"report_internal_inconsistency"),EXACT(E4,"plan_material"),EXACT(E4,"protocol_report"))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(H4,"confirmed_issue"),EXACT(H4,"probable_issue"),EXACT(H4,"not_issue"),EXACT(H4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(I4,"substantive"),EXACT(I4,"minor_presentation"),EXACT(I4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),J4&lt;&gt;"",NOT(OR(EXACT(J4,"direct"),EXACT(J4,"possible"),EXACT(J4,"unlikely"),EXACT(J4,"unknown")))),AND(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material")),NOT(OR(EXACT(K4,"substantive_inconsistency"),EXACT(K4,"minor_presentation"),EXACT(K4,"non_inconsistency"),EXACT(K4,"indeterminate")))),AND(AND(D4="retain",E4="protocol_report"),L4&lt;&gt;"",NOT(OR(EXACT(L4,"substantive_difference"),EXACT(L4,"minor_presentation"),EXACT(L4,"version_timing"),EXACT(L4,"non_inconsistency"),EXACT(L4,"indeterminate"))))),"CHECK FIELDS",IF(AND(F4&lt;&gt;"",NOT(OR(EXACT(F4,"no"),EXACT(F4,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F4,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J4" s="22">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),OR(E4="report_internal_inconsistency",E4="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L4" s="22" t="inlineStr">
+        <is>
+          <t>substantive_difference</t>
+        </is>
+      </c>
+      <c r="M4" s="20" t="n"/>
+      <c r="N4" s="23" t="n"/>
+      <c r="O4" s="23" t="n"/>
+      <c r="P4" s="23" t="n"/>
+      <c r="Q4" s="23" t="n"/>
+      <c r="R4" s="22" t="inlineStr">
+        <is>
+          <t>Every supplied protocol version specifies a mixed model with a random center intercept (synopses pp.10, 56; §11.4.2 pp.39, 86), and the final version adds stroke type as a fixed effect. SAP §5.2 (p.10), main p.4 and the code (Supp5, OCR: lm(fma_affected.Visit_3 ~ fma_affected.Visit_1.cent + medication)) fit baseline FMA and treatment only. Randomization was minimized within center (main p.3), but center is not in the analysis model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1" s="25">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C004</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Secondary missing-data procedures differ from the SAP rule</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>joi250066supp2_prod_1761597796.4701.pdf — p. 5, §4.2: secondary-outcome status; joi250066supp2_prod_1761597796.4701.pdf — p. 11, §6: general imputation rule; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 5, secondary methods: reported nonimputation; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, mRS/PRAI results: affected outcomes; joi250066supp3_prod_1761597796.4701.pdf — p. 7, deviations: mRS death assignment and PRAI exception; joi250066supp3_prod_1761597796.4701.pdf — p. 15, eTable 4: mRS/PRAI results and populations</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G5" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A5="",COUNTIF($A$2:$A$7,A5)&lt;&gt;1,LEFT(A5,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D5="retain",E5="statistical_results")),H5&lt;&gt;"",NOT(EXACT(H5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),I5&lt;&gt;"",NOT(EXACT(I5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),J5&lt;&gt;"",NOT(EXACT(J5,"not_applicable"))),AND(NOT(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material"))),K5&lt;&gt;"",NOT(EXACT(K5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="protocol_report")),L5&lt;&gt;"",NOT(EXACT(L5,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D5,"retain"),EXACT(D5,"exclude"),EXACT(D5,"discuss"))),NOT(OR(EXACT(E5,"statistical_results"),EXACT(E5,"report_internal_inconsistency"),EXACT(E5,"plan_material"),EXACT(E5,"protocol_report"))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(H5,"confirmed_issue"),EXACT(H5,"probable_issue"),EXACT(H5,"not_issue"),EXACT(H5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(I5,"substantive"),EXACT(I5,"minor_presentation"),EXACT(I5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),J5&lt;&gt;"",NOT(OR(EXACT(J5,"direct"),EXACT(J5,"possible"),EXACT(J5,"unlikely"),EXACT(J5,"unknown")))),AND(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material")),NOT(OR(EXACT(K5,"substantive_inconsistency"),EXACT(K5,"minor_presentation"),EXACT(K5,"non_inconsistency"),EXACT(K5,"indeterminate")))),AND(AND(D5="retain",E5="protocol_report"),L5&lt;&gt;"",NOT(OR(EXACT(L5,"substantive_difference"),EXACT(L5,"minor_presentation"),EXACT(L5,"version_timing"),EXACT(L5,"non_inconsistency"),EXACT(L5,"indeterminate"))))),"CHECK FIELDS",IF(AND(F5&lt;&gt;"",NOT(OR(EXACT(F5,"no"),EXACT(F5,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F5,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J5" s="22">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),OR(E5="report_internal_inconsistency",E5="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L5" s="22" t="inlineStr">
+        <is>
+          <t>substantive_difference</t>
+        </is>
+      </c>
+      <c r="M5" s="24" t="n"/>
+      <c r="N5" s="23" t="n"/>
+      <c r="O5" s="23" t="n"/>
+      <c r="P5" s="23" t="n"/>
+      <c r="Q5" s="23" t="n"/>
+      <c r="R5" s="22" t="inlineStr">
+        <is>
+          <t>SAP §6 (p.11): missing secondary outcomes imputed as for the primary analysis (100 MICE imputations); only harm outcomes not imputed. Report (main p.5; Supp3 p.7 deviations) did not impute mRS (deaths set to 6; analysis n=596) or the patient-reported relevance item (PRAI; n=546). Disclosed as SAP deviations in Supp3 p.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92" customHeight="1" s="25">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C005</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Planned primary-endpoint supplementary analyses are not identified in the report</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>joi250066supp1_prod_1761597796.4601.pdf — p. 86, §§11.4.1 and 11.4.3: primary sensitivities and bounded PP context; joi250066supp2_prod_1761597796.4701.pdf — p. 11, §7: center interaction model; joi250066supp2_prod_1761597796.4701.pdf — p. 12, §7.2: seven-variable subgroup package; joi250066supp2_prod_1761597796.4701.pdf — p. 15, addendum: subgroup directions and median splits; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 4, supplementary/post hoc estimands: reported analysis and adherence context; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 5, subgroup/center/spline methods: related reported analyses and prespecification statement; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, primary/sensitivity results: affected primary analysis package; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 7, Additional Post Hoc Analyses: baseline analyses; joi250066supp3_prod_1761597796.4701.pdf — p. 1, complete display index: nine eTables and seven eFigures; joi250066supp3_prod_1761597796.4701.pdf — p. 13, eTable 2: eight prespecified estimands; joi250066supp3_prod_1761597796.4701.pdf — p. 14, eTable 3: post hoc estimands; joi250066supp3_prod_1761597796.4701.pdf — p. 18, eTables 7–8: baseline interaction/spline models; joi250066supp3_prod_1761597796.4701.pdf — p. 25, eFigure 5: center graph; joi250066supp3_prod_1761597796.4701.pdf — p. 27, eFigure 7: post hoc forest</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G6" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A6="",COUNTIF($A$2:$A$7,A6)&lt;&gt;1,LEFT(A6,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D6="retain",E6="statistical_results")),H6&lt;&gt;"",NOT(EXACT(H6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),I6&lt;&gt;"",NOT(EXACT(I6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),J6&lt;&gt;"",NOT(EXACT(J6,"not_applicable"))),AND(NOT(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material"))),K6&lt;&gt;"",NOT(EXACT(K6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="protocol_report")),L6&lt;&gt;"",NOT(EXACT(L6,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D6,"retain"),EXACT(D6,"exclude"),EXACT(D6,"discuss"))),NOT(OR(EXACT(E6,"statistical_results"),EXACT(E6,"report_internal_inconsistency"),EXACT(E6,"plan_material"),EXACT(E6,"protocol_report"))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(H6,"confirmed_issue"),EXACT(H6,"probable_issue"),EXACT(H6,"not_issue"),EXACT(H6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(I6,"substantive"),EXACT(I6,"minor_presentation"),EXACT(I6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),J6&lt;&gt;"",NOT(OR(EXACT(J6,"direct"),EXACT(J6,"possible"),EXACT(J6,"unlikely"),EXACT(J6,"unknown")))),AND(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material")),NOT(OR(EXACT(K6,"substantive_inconsistency"),EXACT(K6,"minor_presentation"),EXACT(K6,"non_inconsistency"),EXACT(K6,"indeterminate")))),AND(AND(D6="retain",E6="protocol_report"),L6&lt;&gt;"",NOT(OR(EXACT(L6,"substantive_difference"),EXACT(L6,"minor_presentation"),EXACT(L6,"version_timing"),EXACT(L6,"non_inconsistency"),EXACT(L6,"indeterminate"))))),"CHECK FIELDS",IF(AND(F6&lt;&gt;"",NOT(OR(EXACT(F6,"no"),EXACT(F6,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F6,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J6" s="22">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),OR(E6="report_internal_inconsistency",E6="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>substantive_difference</t>
+        </is>
+      </c>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="23" t="n"/>
+      <c r="O6" s="23" t="n"/>
+      <c r="P6" s="23" t="n"/>
+      <c r="Q6" s="23" t="n"/>
+      <c r="R6" s="22" t="inlineStr">
+        <is>
+          <t>Not found in any report document (main article; Supp3 index of 9 eTables and 7 eFigures; Supp4 is the investigator list): SAP §7 center and treatment-by-center interaction model, SAP §7.2 seven prespecified subgroup interactions with forest plot (ICEMAN addendum pp.14-15), protocol §11.4.3(b) treatment x stroke type and (c) added-covariable analyses. Planned analyses reported as 'post hoc': center plot (eFigure 5) and the protocol per-protocol set (estimand 11). Main p.5 says prespecified analyses were performed as outlined in the SAP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1" s="25">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C006</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Serious-event hierarchy counts do not reconcile with their parent totals</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, Table 2, levodopa serious-event parent and all 13 top-level category rows; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, Table 2, placebo infection parent and all six infection subtype rows; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, Adverse Events narrative and table notes: corroborating event totals and unit context</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G7" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A7="",COUNTIF($A$2:$A$7,A7)&lt;&gt;1,LEFT(A7,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D7="retain",E7="statistical_results")),H7&lt;&gt;"",NOT(EXACT(H7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),I7&lt;&gt;"",NOT(EXACT(I7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),J7&lt;&gt;"",NOT(EXACT(J7,"not_applicable"))),AND(NOT(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material"))),K7&lt;&gt;"",NOT(EXACT(K7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="protocol_report")),L7&lt;&gt;"",NOT(EXACT(L7,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D7,"retain"),EXACT(D7,"exclude"),EXACT(D7,"discuss"))),NOT(OR(EXACT(E7,"statistical_results"),EXACT(E7,"report_internal_inconsistency"),EXACT(E7,"plan_material"),EXACT(E7,"protocol_report"))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(H7,"confirmed_issue"),EXACT(H7,"probable_issue"),EXACT(H7,"not_issue"),EXACT(H7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(I7,"substantive"),EXACT(I7,"minor_presentation"),EXACT(I7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),J7&lt;&gt;"",NOT(OR(EXACT(J7,"direct"),EXACT(J7,"possible"),EXACT(J7,"unlikely"),EXACT(J7,"unknown")))),AND(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material")),NOT(OR(EXACT(K7,"substantive_inconsistency"),EXACT(K7,"minor_presentation"),EXACT(K7,"non_inconsistency"),EXACT(K7,"indeterminate")))),AND(AND(D7="retain",E7="protocol_report"),L7&lt;&gt;"",NOT(OR(EXACT(L7,"substantive_difference"),EXACT(L7,"minor_presentation"),EXACT(L7,"version_timing"),EXACT(L7,"non_inconsistency"),EXACT(L7,"indeterminate"))))),"CHECK FIELDS",IF(AND(F7&lt;&gt;"",NOT(OR(EXACT(F7,"no"),EXACT(F7,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F7,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>indeterminate</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),OR(E7="report_internal_inconsistency",E7="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L7" s="22">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M7" s="24" t="n"/>
+      <c r="N7" s="23" t="n"/>
+      <c r="O7" s="23" t="n"/>
+      <c r="P7" s="23" t="n"/>
+      <c r="Q7" s="23" t="n"/>
+      <c r="R7" s="22" t="inlineStr">
+        <is>
+          <t>Table 2 (main p.6, rendered): levodopa SAE categories sum to 143 vs 126 events (placebo 139 vs 129); infection subtypes sum to 59 vs 55 (levodopa) and 52 vs 44 (placebo). Stroke and cardiac subtypes and the prespecified-AE block (79, 67) reconcile exactly. Fall, fracture and trauma rows suggest events can carry several categories, but no note says so; only stroke subtypes are indented. Cannot decide whether this is an error or unstated multiple classification.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R7"/>
+  <conditionalFormatting sqref="H2:H7">
+    <cfRule type="expression" priority="8" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I7">
+    <cfRule type="expression" priority="9" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J7">
+    <cfRule type="expression" priority="10" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K7">
+    <cfRule type="expression" priority="11" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),OR($E2="report_internal_inconsistency",$E2="plan_material")))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L7">
+    <cfRule type="expression" priority="12" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="protocol_report"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G7">
+    <cfRule type="expression" priority="13" dxfId="71">
+      <formula>G2&lt;&gt;"PRIMARY READY"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="8">
+    <dataValidation sqref="D2:D7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"retain,exclude,discuss"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"statistical_results,report_internal_inconsistency,plan_material,protocol_report"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"no,primary_done"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"confirmed_issue,probable_issue,not_issue,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive,minor_presentation,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"direct,possible,unlikely,unknown,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive_inconsistency,minor_presentation,non_inconsistency,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive_difference,minor_presentation,version_timing,non_inconsistency,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
